--- a/Deliverables/Engineering/SoftwareComponentVerificationAndIntegrationVerification/ENG-SWE5-003_SW 통합시험 결과서.xlsx
+++ b/Deliverables/Engineering/SoftwareComponentVerificationAndIntegrationVerification/ENG-SWE5-003_SW 통합시험 결과서.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1402,14 +1402,15 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NotImplementedError 발생 관측</t>
+          <t>leftCommand=rightCommand=RELEASE, blocked=False 관측 — Phase2 계약(문별 최소-priority 선택)으로 정상 처리 확인(Phase1 NotImplementedError 계약은 완전히 대체됨)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>tests_integration/test_it_step4_*.py (unittest 실행, 2026-09-18) + coverage_it.json</t>
-        </is>
-      </c>
+          <t>tests_integration/test_it_step4_*.py (unittest 실행, 2026-09-19) + coverage_it.json (test_it_step4_command_arbiter.py, 2026-09-19 갱신)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>해당 없음(Pass)</t>
@@ -2147,6 +2148,1656 @@
         </is>
       </c>
       <c r="G52" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="42" t="inlineStr">
+        <is>
+          <t>IT-0044</t>
+        </is>
+      </c>
+      <c r="B53" s="42" t="inlineStr">
+        <is>
+          <t>IF-0016</t>
+        </is>
+      </c>
+      <c r="C53" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D53" s="42" t="inlineStr">
+        <is>
+          <t>CrashEvaluationResult(status=CONFIRMED, releaseCandidate(BOTH,RELEASE,priority=1,CRASH_CONFIRMED), pendingHoldApplied=False) 관측</t>
+        </is>
+      </c>
+      <c r="E53" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step8_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F53" s="42" t="inlineStr"/>
+      <c r="G53" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="42" t="inlineStr">
+        <is>
+          <t>IT-0045</t>
+        </is>
+      </c>
+      <c r="B54" s="42" t="inlineStr">
+        <is>
+          <t>IF-0016</t>
+        </is>
+      </c>
+      <c r="C54" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D54" s="42" t="inlineStr">
+        <is>
+          <t>releaseCandidate=None, pendingHoldApplied=True 관측 — SWR-008 보류 확인</t>
+        </is>
+      </c>
+      <c r="E54" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step8_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F54" s="42" t="inlineStr"/>
+      <c r="G54" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="42" t="inlineStr">
+        <is>
+          <t>IT-0046</t>
+        </is>
+      </c>
+      <c r="B55" s="42" t="inlineStr">
+        <is>
+          <t>IF-0016</t>
+        </is>
+      </c>
+      <c r="C55" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D55" s="42" t="inlineStr">
+        <is>
+          <t>status=NONE, releaseCandidate=None 관측</t>
+        </is>
+      </c>
+      <c r="E55" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step8_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F55" s="42" t="inlineStr"/>
+      <c r="G55" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="42" t="inlineStr">
+        <is>
+          <t>IT-0047</t>
+        </is>
+      </c>
+      <c r="B56" s="42" t="inlineStr">
+        <is>
+          <t>IF-0016</t>
+        </is>
+      </c>
+      <c r="C56" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D56" s="42" t="inlineStr">
+        <is>
+          <t>예외 없이 status=NONE 관측 — 무효 필드 방어적 처리 확인</t>
+        </is>
+      </c>
+      <c r="E56" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step8_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F56" s="42" t="inlineStr"/>
+      <c r="G56" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="42" t="inlineStr">
+        <is>
+          <t>IT-0048</t>
+        </is>
+      </c>
+      <c r="B57" s="42" t="inlineStr">
+        <is>
+          <t>IF-0016</t>
+        </is>
+      </c>
+      <c r="C57" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D57" s="42" t="inlineStr">
+        <is>
+          <t>ValueError 발생 관측 — 방어적 계약 확인</t>
+        </is>
+      </c>
+      <c r="E57" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step8_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F57" s="42" t="inlineStr"/>
+      <c r="G57" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="42" t="inlineStr">
+        <is>
+          <t>IT-0049</t>
+        </is>
+      </c>
+      <c r="B58" s="42" t="inlineStr">
+        <is>
+          <t>IF-0017</t>
+        </is>
+      </c>
+      <c r="C58" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D58" s="42" t="inlineStr">
+        <is>
+          <t>leftRiskActive=rightRiskActive=False, 후보 없음 관측(FF)</t>
+        </is>
+      </c>
+      <c r="E58" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step9_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F58" s="42" t="inlineStr"/>
+      <c r="G58" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="42" t="inlineStr">
+        <is>
+          <t>IT-0050</t>
+        </is>
+      </c>
+      <c r="B59" s="42" t="inlineStr">
+        <is>
+          <t>IF-0017</t>
+        </is>
+      </c>
+      <c r="C59" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D59" s="42" t="inlineStr">
+        <is>
+          <t>leftSuppressCandidate(LEFT,LOCK,priority=2,APPROACH_RISK_LEFT), rightSuppressCandidate=None 관측(FT)</t>
+        </is>
+      </c>
+      <c r="E59" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step9_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F59" s="42" t="inlineStr"/>
+      <c r="G59" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="42" t="inlineStr">
+        <is>
+          <t>IT-0051</t>
+        </is>
+      </c>
+      <c r="B60" s="42" t="inlineStr">
+        <is>
+          <t>IF-0017</t>
+        </is>
+      </c>
+      <c r="C60" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D60" s="42" t="inlineStr">
+        <is>
+          <t>rightSuppressCandidate(RIGHT,LOCK,APPROACH_RISK_RIGHT), leftSuppressCandidate=None 관측(TF)</t>
+        </is>
+      </c>
+      <c r="E60" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step9_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F60" s="42" t="inlineStr"/>
+      <c r="G60" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="42" t="inlineStr">
+        <is>
+          <t>IT-0052</t>
+        </is>
+      </c>
+      <c r="B61" s="42" t="inlineStr">
+        <is>
+          <t>IF-0017</t>
+        </is>
+      </c>
+      <c r="C61" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D61" s="42" t="inlineStr">
+        <is>
+          <t>좌/우 각각 독립 후보 생성 관측(TT)</t>
+        </is>
+      </c>
+      <c r="E61" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step9_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F61" s="42" t="inlineStr"/>
+      <c r="G61" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="42" t="inlineStr">
+        <is>
+          <t>IT-0053</t>
+        </is>
+      </c>
+      <c r="B62" s="42" t="inlineStr">
+        <is>
+          <t>IF-0017</t>
+        </is>
+      </c>
+      <c r="C62" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D62" s="42" t="inlineStr">
+        <is>
+          <t>예외 없이 leftRiskActive=False 관측 — 무효 필드 방어적 처리 확인</t>
+        </is>
+      </c>
+      <c r="E62" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step9_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F62" s="42" t="inlineStr"/>
+      <c r="G62" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="42" t="inlineStr">
+        <is>
+          <t>IT-0054</t>
+        </is>
+      </c>
+      <c r="B63" s="42" t="inlineStr">
+        <is>
+          <t>IF-0017</t>
+        </is>
+      </c>
+      <c r="C63" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D63" s="42" t="inlineStr">
+        <is>
+          <t>ValueError 발생 관측 — 방어적 계약 확인</t>
+        </is>
+      </c>
+      <c r="E63" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step9_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F63" s="42" t="inlineStr"/>
+      <c r="G63" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="42" t="inlineStr">
+        <is>
+          <t>IT-0055</t>
+        </is>
+      </c>
+      <c r="B64" s="42" t="inlineStr">
+        <is>
+          <t>IF-0018</t>
+        </is>
+      </c>
+      <c r="C64" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D64" s="42" t="inlineStr">
+        <is>
+          <t>leftOverrideActive=False 관측(재입력 신호 없음)</t>
+        </is>
+      </c>
+      <c r="E64" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step10_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F64" s="42" t="inlineStr"/>
+      <c r="G64" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="42" t="inlineStr">
+        <is>
+          <t>IT-0056</t>
+        </is>
+      </c>
+      <c r="B65" s="42" t="inlineStr">
+        <is>
+          <t>IF-0018</t>
+        </is>
+      </c>
+      <c r="C65" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D65" s="42" t="inlineStr">
+        <is>
+          <t>정확히 10.0초 경과 시점 leftOverrideActive=True, reasonCode=APPROACH_RISK_OVERRIDE_LEFT 관측 — 경계값(&lt;=10s) 확인</t>
+        </is>
+      </c>
+      <c r="E65" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step10_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F65" s="42" t="inlineStr"/>
+      <c r="G65" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="42" t="inlineStr">
+        <is>
+          <t>IT-0057</t>
+        </is>
+      </c>
+      <c r="B66" s="42" t="inlineStr">
+        <is>
+          <t>IF-0018</t>
+        </is>
+      </c>
+      <c r="C66" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D66" s="42" t="inlineStr">
+        <is>
+          <t>10.1초 경과 시점 leftOverrideActive=False 관측 — 경계값(초과) 확인</t>
+        </is>
+      </c>
+      <c r="E66" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step10_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F66" s="42" t="inlineStr"/>
+      <c r="G66" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="42" t="inlineStr">
+        <is>
+          <t>IT-0058</t>
+        </is>
+      </c>
+      <c r="B67" s="42" t="inlineStr">
+        <is>
+          <t>IF-0018</t>
+        </is>
+      </c>
+      <c r="C67" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D67" s="42" t="inlineStr">
+        <is>
+          <t>riskActive=False에서 leftOverrideActive=False, 타이머 리셋 관측</t>
+        </is>
+      </c>
+      <c r="E67" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step10_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F67" s="42" t="inlineStr"/>
+      <c r="G67" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="42" t="inlineStr">
+        <is>
+          <t>IT-0059</t>
+        </is>
+      </c>
+      <c r="B68" s="42" t="inlineStr">
+        <is>
+          <t>IF-0018</t>
+        </is>
+      </c>
+      <c r="C68" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D68" s="42" t="inlineStr">
+        <is>
+          <t>leftOverrideActive=True, rightOverrideActive=False 관측 — 좌우 독립성 확인</t>
+        </is>
+      </c>
+      <c r="E68" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step10_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F68" s="42" t="inlineStr"/>
+      <c r="G68" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="42" t="inlineStr">
+        <is>
+          <t>IT-0060</t>
+        </is>
+      </c>
+      <c r="B69" s="42" t="inlineStr">
+        <is>
+          <t>IF-0018</t>
+        </is>
+      </c>
+      <c r="C69" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D69" s="42" t="inlineStr">
+        <is>
+          <t>재진입 후 9초 경과 시점 override 성립 관측 — 새 10초 윈도우 시작 확인</t>
+        </is>
+      </c>
+      <c r="E69" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step10_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F69" s="42" t="inlineStr"/>
+      <c r="G69" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="42" t="inlineStr">
+        <is>
+          <t>IT-0061</t>
+        </is>
+      </c>
+      <c r="B70" s="42" t="inlineStr">
+        <is>
+          <t>IF-0018</t>
+        </is>
+      </c>
+      <c r="C70" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D70" s="42" t="inlineStr">
+        <is>
+          <t>reset() 후 즉시 재입력에도 override 성립 관측 — 타이머 초기화 확인</t>
+        </is>
+      </c>
+      <c r="E70" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step10_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F70" s="42" t="inlineStr"/>
+      <c r="G70" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="42" t="inlineStr">
+        <is>
+          <t>IT-0062</t>
+        </is>
+      </c>
+      <c r="B71" s="42" t="inlineStr">
+        <is>
+          <t>IF-0019</t>
+        </is>
+      </c>
+      <c r="C71" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D71" s="42" t="inlineStr">
+        <is>
+          <t>triggered=True, reasonCodes=[FIRE_DETECTED] 관측</t>
+        </is>
+      </c>
+      <c r="E71" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step11_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F71" s="42" t="inlineStr"/>
+      <c r="G71" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="42" t="inlineStr">
+        <is>
+          <t>IT-0063</t>
+        </is>
+      </c>
+      <c r="B72" s="42" t="inlineStr">
+        <is>
+          <t>IF-0019</t>
+        </is>
+      </c>
+      <c r="C72" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D72" s="42" t="inlineStr">
+        <is>
+          <t>triggered=True, reasonCodes=[OVERTEMPERATURE_DETECTED] 관측</t>
+        </is>
+      </c>
+      <c r="E72" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step11_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F72" s="42" t="inlineStr"/>
+      <c r="G72" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="42" t="inlineStr">
+        <is>
+          <t>IT-0064</t>
+        </is>
+      </c>
+      <c r="B73" s="42" t="inlineStr">
+        <is>
+          <t>IF-0019</t>
+        </is>
+      </c>
+      <c r="C73" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D73" s="42" t="inlineStr">
+        <is>
+          <t>triggered=True, reasonCodes=[ADULT_PRESENT_DETECTED] 관측</t>
+        </is>
+      </c>
+      <c r="E73" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step11_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F73" s="42" t="inlineStr"/>
+      <c r="G73" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="42" t="inlineStr">
+        <is>
+          <t>IT-0065</t>
+        </is>
+      </c>
+      <c r="B74" s="42" t="inlineStr">
+        <is>
+          <t>IF-0019</t>
+        </is>
+      </c>
+      <c r="C74" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D74" s="42" t="inlineStr">
+        <is>
+          <t>reasonCodes=[FIRE_DETECTED,OVERTEMPERATURE_DETECTED,ADULT_PRESENT_DETECTED] 순서대로 전부 관측</t>
+        </is>
+      </c>
+      <c r="E74" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step11_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F74" s="42" t="inlineStr"/>
+      <c r="G74" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="42" t="inlineStr">
+        <is>
+          <t>IT-0066</t>
+        </is>
+      </c>
+      <c r="B75" s="42" t="inlineStr">
+        <is>
+          <t>IF-0019</t>
+        </is>
+      </c>
+      <c r="C75" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D75" s="42" t="inlineStr">
+        <is>
+          <t>triggered=False, releaseCandidate=None, reasonCodes=[] 관측</t>
+        </is>
+      </c>
+      <c r="E75" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step11_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F75" s="42" t="inlineStr"/>
+      <c r="G75" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="42" t="inlineStr">
+        <is>
+          <t>IT-0067</t>
+        </is>
+      </c>
+      <c r="B76" s="42" t="inlineStr">
+        <is>
+          <t>IF-0019</t>
+        </is>
+      </c>
+      <c r="C76" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D76" s="42" t="inlineStr">
+        <is>
+          <t>예외 없이 triggered=False(fire 미기여) 관측 — 무효 필드 방어적 처리 확인</t>
+        </is>
+      </c>
+      <c r="E76" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step11_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F76" s="42" t="inlineStr"/>
+      <c r="G76" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="42" t="inlineStr">
+        <is>
+          <t>IT-0068</t>
+        </is>
+      </c>
+      <c r="B77" s="42" t="inlineStr">
+        <is>
+          <t>IF-0019</t>
+        </is>
+      </c>
+      <c r="C77" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D77" s="42" t="inlineStr">
+        <is>
+          <t>ValueError 발생 관측 — 방어적 계약 확인</t>
+        </is>
+      </c>
+      <c r="E77" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step11_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F77" s="42" t="inlineStr"/>
+      <c r="G77" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="42" t="inlineStr">
+        <is>
+          <t>IT-0069</t>
+        </is>
+      </c>
+      <c r="B78" s="42" t="inlineStr">
+        <is>
+          <t>IF-0008</t>
+        </is>
+      </c>
+      <c r="C78" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D78" s="42" t="inlineStr">
+        <is>
+          <t>leftCommand=rightCommand=RELEASE, reasonCode=CRASH_CONFIRMED 관측 — priority=1 승리 확인</t>
+        </is>
+      </c>
+      <c r="E78" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step12_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F78" s="42" t="inlineStr"/>
+      <c r="G78" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="42" t="inlineStr">
+        <is>
+          <t>IT-0070</t>
+        </is>
+      </c>
+      <c r="B79" s="42" t="inlineStr">
+        <is>
+          <t>IF-0008</t>
+        </is>
+      </c>
+      <c r="C79" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D79" s="42" t="inlineStr">
+        <is>
+          <t>leftCommand=LOCK(APPROACH_RISK_LEFT), rightCommand=RELEASE(FORCED_RELEASE) 관측 — priority=2 vs 3 확인</t>
+        </is>
+      </c>
+      <c r="E79" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step12_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F79" s="42" t="inlineStr"/>
+      <c r="G79" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="42" t="inlineStr">
+        <is>
+          <t>IT-0071</t>
+        </is>
+      </c>
+      <c r="B80" s="42" t="inlineStr">
+        <is>
+          <t>IF-0008</t>
+        </is>
+      </c>
+      <c r="C80" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D80" s="42" t="inlineStr">
+        <is>
+          <t>leftCommand=LOCK, rightCommand=NO_CHANGE 관측 — 문별 독립성 확인</t>
+        </is>
+      </c>
+      <c r="E80" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step12_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F80" s="42" t="inlineStr"/>
+      <c r="G80" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="42" t="inlineStr">
+        <is>
+          <t>IT-0072</t>
+        </is>
+      </c>
+      <c r="B81" s="42" t="inlineStr">
+        <is>
+          <t>IF-0008</t>
+        </is>
+      </c>
+      <c r="C81" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D81" s="42" t="inlineStr">
+        <is>
+          <t>ValueError 발생 관측 — 동일 priority 충돌 불변조건 확인</t>
+        </is>
+      </c>
+      <c r="E81" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step12_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F81" s="42" t="inlineStr"/>
+      <c r="G81" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="42" t="inlineStr">
+        <is>
+          <t>IT-0073</t>
+        </is>
+      </c>
+      <c r="B82" s="42" t="inlineStr">
+        <is>
+          <t>IF-0008</t>
+        </is>
+      </c>
+      <c r="C82" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D82" s="42" t="inlineStr">
+        <is>
+          <t>blocked=True/STATE_FAULT 관측 — Phase2 후보 전부 차단 확인(1~4단계 회귀 없음)</t>
+        </is>
+      </c>
+      <c r="E82" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step12_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F82" s="42" t="inlineStr"/>
+      <c r="G82" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="42" t="inlineStr">
+        <is>
+          <t>IT-0074</t>
+        </is>
+      </c>
+      <c r="B83" s="42" t="inlineStr">
+        <is>
+          <t>IF-0008</t>
+        </is>
+      </c>
+      <c r="C83" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D83" s="42" t="inlineStr">
+        <is>
+          <t>blocked=True/INPUT_INVALID 관측 — Phase2 후보 전부 차단 확인(1~4단계 회귀 없음)</t>
+        </is>
+      </c>
+      <c r="E83" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step12_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F83" s="42" t="inlineStr"/>
+      <c r="G83" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="42" t="inlineStr">
+        <is>
+          <t>IT-0075</t>
+        </is>
+      </c>
+      <c r="B84" s="42" t="inlineStr">
+        <is>
+          <t>IF-0013</t>
+        </is>
+      </c>
+      <c r="C84" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D84" s="42" t="inlineStr">
+        <is>
+          <t>valid=True, value=CrashStatus.CONFIRMED 관측</t>
+        </is>
+      </c>
+      <c r="E84" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step13_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F84" s="42" t="inlineStr"/>
+      <c r="G84" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="42" t="inlineStr">
+        <is>
+          <t>IT-0076</t>
+        </is>
+      </c>
+      <c r="B85" s="42" t="inlineStr">
+        <is>
+          <t>IF-0013</t>
+        </is>
+      </c>
+      <c r="C85" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D85" s="42" t="inlineStr">
+        <is>
+          <t>valid=False, errorReason=INVALID_ENUM_VALUE 관측</t>
+        </is>
+      </c>
+      <c r="E85" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step13_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F85" s="42" t="inlineStr"/>
+      <c r="G85" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="42" t="inlineStr">
+        <is>
+          <t>IT-0077</t>
+        </is>
+      </c>
+      <c r="B86" s="42" t="inlineStr">
+        <is>
+          <t>IF-0013</t>
+        </is>
+      </c>
+      <c r="C86" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D86" s="42" t="inlineStr">
+        <is>
+          <t>valid=False, errorReason=MISSING 관측</t>
+        </is>
+      </c>
+      <c r="E86" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step13_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F86" s="42" t="inlineStr"/>
+      <c r="G86" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="42" t="inlineStr">
+        <is>
+          <t>IT-0078</t>
+        </is>
+      </c>
+      <c r="B87" s="42" t="inlineStr">
+        <is>
+          <t>IF-0013</t>
+        </is>
+      </c>
+      <c r="C87" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D87" s="42" t="inlineStr">
+        <is>
+          <t>valid=False, errorReason=TYPE_ERROR 관측</t>
+        </is>
+      </c>
+      <c r="E87" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step13_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F87" s="42" t="inlineStr"/>
+      <c r="G87" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="42" t="inlineStr">
+        <is>
+          <t>IT-0079</t>
+        </is>
+      </c>
+      <c r="B88" s="42" t="inlineStr">
+        <is>
+          <t>IF-0014</t>
+        </is>
+      </c>
+      <c r="C88" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D88" s="42" t="inlineStr">
+        <is>
+          <t>left valid=True/value=True, right valid=True/value=False 독립 관측</t>
+        </is>
+      </c>
+      <c r="E88" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step13_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F88" s="42" t="inlineStr"/>
+      <c r="G88" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="42" t="inlineStr">
+        <is>
+          <t>IT-0080</t>
+        </is>
+      </c>
+      <c r="B89" s="42" t="inlineStr">
+        <is>
+          <t>IF-0015</t>
+        </is>
+      </c>
+      <c r="C89" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D89" s="42" t="inlineStr">
+        <is>
+          <t>valid=False, errorReason=TYPE_ERROR 관측</t>
+        </is>
+      </c>
+      <c r="E89" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step13_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F89" s="42" t="inlineStr"/>
+      <c r="G89" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="42" t="inlineStr">
+        <is>
+          <t>IT-0081</t>
+        </is>
+      </c>
+      <c r="B90" s="42" t="inlineStr">
+        <is>
+          <t>IF-0005</t>
+        </is>
+      </c>
+      <c r="C90" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D90" s="42" t="inlineStr">
+        <is>
+          <t>9필드 모두 정상 조립, Phase1 3필드 정규화 결과 불변 관측 — 회귀 없음 확인</t>
+        </is>
+      </c>
+      <c r="E90" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step13_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F90" s="42" t="inlineStr"/>
+      <c r="G90" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="42" t="inlineStr">
+        <is>
+          <t>IT-0082</t>
+        </is>
+      </c>
+      <c r="B91" s="42" t="inlineStr">
+        <is>
+          <t>IF-0016</t>
+        </is>
+      </c>
+      <c r="C91" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D91" s="42" t="inlineStr">
+        <is>
+          <t>errorOccurred=False, confirmedOutput=(RELEASE,RELEASE) 관측(전체 체인)</t>
+        </is>
+      </c>
+      <c r="E91" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step14_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F91" s="42" t="inlineStr"/>
+      <c r="G91" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="42" t="inlineStr">
+        <is>
+          <t>IT-0083</t>
+        </is>
+      </c>
+      <c r="B92" s="42" t="inlineStr">
+        <is>
+          <t>IF-0017</t>
+        </is>
+      </c>
+      <c r="C92" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D92" s="42" t="inlineStr">
+        <is>
+          <t>errorOccurred=False, confirmedOutput=(LOCK,LOCK) 관측(전체 체인, 좌우 독립 억제)</t>
+        </is>
+      </c>
+      <c r="E92" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step14_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F92" s="42" t="inlineStr"/>
+      <c r="G92" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="42" t="inlineStr">
+        <is>
+          <t>IT-0084</t>
+        </is>
+      </c>
+      <c r="B93" s="42" t="inlineStr">
+        <is>
+          <t>IF-0018</t>
+        </is>
+      </c>
+      <c r="C93" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D93" s="42" t="inlineStr">
+        <is>
+          <t>15초 경과에도 confirmedOutput.left=LOCK 유지 관측 — placeholder 한계(override 불성립) 문서화 확인</t>
+        </is>
+      </c>
+      <c r="E93" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step14_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F93" s="42" t="inlineStr"/>
+      <c r="G93" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="42" t="inlineStr">
+        <is>
+          <t>IT-0085</t>
+        </is>
+      </c>
+      <c r="B94" s="42" t="inlineStr">
+        <is>
+          <t>IF-0019</t>
+        </is>
+      </c>
+      <c r="C94" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D94" s="42" t="inlineStr">
+        <is>
+          <t>errorOccurred=False, confirmedOutput=(RELEASE,RELEASE) 관측(전체 체인)</t>
+        </is>
+      </c>
+      <c r="E94" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step14_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F94" s="42" t="inlineStr"/>
+      <c r="G94" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="42" t="inlineStr">
+        <is>
+          <t>IT-0086</t>
+        </is>
+      </c>
+      <c r="B95" s="42" t="inlineStr">
+        <is>
+          <t>IF-0016~IF-0019,IF-0008</t>
+        </is>
+      </c>
+      <c r="C95" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D95" s="42" t="inlineStr">
+        <is>
+          <t>confirmedOutput=(RELEASE,RELEASE) 관측 — 충돌(priority=1) 우선 적용 확인(7장 시나리오7 재현)</t>
+        </is>
+      </c>
+      <c r="E95" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step14_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F95" s="42" t="inlineStr"/>
+      <c r="G95" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="42" t="inlineStr">
+        <is>
+          <t>IT-0087</t>
+        </is>
+      </c>
+      <c r="B96" s="42" t="inlineStr">
+        <is>
+          <t>IF-0006~IF-0019</t>
+        </is>
+      </c>
+      <c r="C96" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D96" s="42" t="inlineStr">
+        <is>
+          <t>callLog=[IF-0006,IF-0007,IF-0016,IF-0017,IF-0018,IF-0019,IF-0008,IF-0009,IF-0010,IF-0011,IF-0012] 관측 — 고정 순서 확인</t>
+        </is>
+      </c>
+      <c r="E96" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step14_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F96" s="42" t="inlineStr"/>
+      <c r="G96" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="42" t="inlineStr">
+        <is>
+          <t>IT-0088</t>
+        </is>
+      </c>
+      <c r="B97" s="42" t="inlineStr">
+        <is>
+          <t>IF-0007~IF-0009,IF-0016</t>
+        </is>
+      </c>
+      <c r="C97" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D97" s="42" t="inlineStr">
+        <is>
+          <t>state=FAULT, confirmedOutput=(LOCK,LOCK) 관측 — FAULT가 crash 후보보다 우선 확인</t>
+        </is>
+      </c>
+      <c r="E97" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step14_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F97" s="42" t="inlineStr"/>
+      <c r="G97" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="42" t="inlineStr">
+        <is>
+          <t>IT-0089</t>
+        </is>
+      </c>
+      <c r="B98" s="42" t="inlineStr">
+        <is>
+          <t>IF-0006,IF-0007,IF-0016</t>
+        </is>
+      </c>
+      <c r="C98" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D98" s="42" t="inlineStr">
+        <is>
+          <t>state=DEGRADED, confirmedOutput=(RELEASE,RELEASE) 관측 — DEGRADED가 Phase2 후보를 차단하지 않음 확인</t>
+        </is>
+      </c>
+      <c r="E98" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step14_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F98" s="42" t="inlineStr"/>
+      <c r="G98" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="42" t="inlineStr">
+        <is>
+          <t>IT-0090</t>
+        </is>
+      </c>
+      <c r="B99" s="42" t="inlineStr">
+        <is>
+          <t>IF-0001,IF-0002,IF-0005,IF-0007,IF-0009</t>
+        </is>
+      </c>
+      <c r="C99" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D99" s="42" t="inlineStr">
+        <is>
+          <t>state=FAULT, warningReasonCode 비공백, confirmedOutput=(LOCK,LOCK) 관측 — Phase1 인수기준 회귀 없음 확인</t>
+        </is>
+      </c>
+      <c r="E99" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step14_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F99" s="42" t="inlineStr"/>
+      <c r="G99" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="42" t="inlineStr">
+        <is>
+          <t>IT-0091</t>
+        </is>
+      </c>
+      <c r="B100" s="42" t="inlineStr">
+        <is>
+          <t>IF-0018</t>
+        </is>
+      </c>
+      <c r="C100" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D100" s="42" t="inlineStr">
+        <is>
+          <t>callLog=[IF-0018-RESET] 관측 — orchestrator.reset()의 overrideManager.reset() 호출 확인</t>
+        </is>
+      </c>
+      <c r="E100" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step14_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F100" s="42" t="inlineStr"/>
+      <c r="G100" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="42" t="inlineStr">
+        <is>
+          <t>IT-0092</t>
+        </is>
+      </c>
+      <c r="B101" s="42" t="inlineStr">
+        <is>
+          <t>IF-0005,IF-0008</t>
+        </is>
+      </c>
+      <c r="C101" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D101" s="42" t="inlineStr">
+        <is>
+          <t>confirmedOutput=(RELEASE,RELEASE) 관측 — 무관한 fire 필드 무효가 crash 후보를 차단하지 않음 확인(결정표 D 근거)</t>
+        </is>
+      </c>
+      <c r="E101" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step14_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F101" s="42" t="inlineStr"/>
+      <c r="G101" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="42" t="inlineStr">
+        <is>
+          <t>IT-0093</t>
+        </is>
+      </c>
+      <c r="B102" s="42" t="inlineStr">
+        <is>
+          <t>IF-0013</t>
+        </is>
+      </c>
+      <c r="C102" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D102" s="42" t="inlineStr">
+        <is>
+          <t>valid=True, value=CrashStatus.PENDING 관측 — 이미 파싱된 enum 인스턴스 수용 확인</t>
+        </is>
+      </c>
+      <c r="E102" s="42" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step13_*.py (unittest 실행, 2026-09-19) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="F102" s="42" t="inlineStr"/>
+      <c r="G102" s="42" t="inlineStr">
         <is>
           <t>해당 없음(Pass)</t>
         </is>
@@ -2179,7 +3830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2386,6 +4037,47 @@
       <c r="I10" s="42" t="inlineStr">
         <is>
           <t>함수 커버리지 100%(31/31, class 선언 제외), 문 커버리지 100%(232/232), 분기 커버리지 100%(34/34) — coverage.py --branch, coverage_it.json. Call 커버리지: IF-0005~IF-0009 5개 인터페이스 7개 호출지점은 coverage.py 줄 단위 실행 확인(AST ast.Call 매칭)으로 100% 직접 실측. IF-0010/IF-0011/IF-0012 3개 호출지점은 동일 for 루프 내 람다-튜플 표현식에 위치해 coverage.py가 물리적 줄을 개별 statement로 추적하지 못하는 도구 한계(최소 재현 사례로 확인, ENG-SWE5-001 12장)가 있어, IT-0029(recordCalls 실물 계측)·IT-0031(오류주입 관측)로 실제 호출을 직접 증명해 보완 — 9/9 아키텍처 호출관계(IF-0005~IF-0012) 전부 실행 확인. IF-0001~IF-0004(외부 경계)는 Phase1 실제 I/O 없음(스텁)이라 인프로세스 호출지점이 존재하지 않으며, 어댑터 왕복 변환 무결성(IT-0021~0024)과 원시입력 경로 시험(IT-0034~0043)으로 대체 검증. 적용 한계(12장): source_timestamp_s 상한 확인 필요(범위 판정식 미확정으로 상한 경계값시험 미실시), DEGRADED/FAULT 즉시 전이(hysteresis 미적용 가정) 재검증 필요, Command Arbiter 우선순위 규칙 체인은 Phase2+ 범위(candidateCommands 항상 빈 리스트), OEM-IF-005/006 실제 통신 프로토콜(CAN/LIN/HTTP)과 HIL/실차 통합은 SYS.4/향후 Phase 범위.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>RUN-SWE5-002</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C11" s="42" t="inlineStr">
+        <is>
+          <t>ENG-SWE2-001 v0.2(Draft) / ENG-SWE3-001 v0.2(구현 기준, coding 2026-09-19 커밋 — 154개 단위+통합+시스템 회귀 전량 Pass 확인 후 본 게이트 착수)</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="inlineStr">
+        <is>
+          <t>Python 3.14(런타임 실측), unittest + coverage.py 7.11.0 + radon 6.0.1, tests_integration/(신규 8~14단계 파일 test_it_step8_*~test_it_step14_*.py 포함)</t>
+        </is>
+      </c>
+      <c r="E11" s="42" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" s="42" t="n">
+        <v>50</v>
+      </c>
+      <c r="G11" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" s="42" t="inlineStr">
+        <is>
+          <t>함수 커버리지 100%(47/47, 이번 통합 범위 src/ngv 전체 — Phase1 31개+Phase2 신규/갱신 16개 함수, class 선언 제외). 문 커버리지 100%(411/411), 분기 커버리지 100%(76/76) — coverage.py --branch, coverage_it.json(tests_integration/ 93개 케이스 전량 실행 기준, Phase1 43 + Phase2 50). Call 커버리지: AST 매칭 48개 호출지점 중 45개(93.75%)는 coverage.py 줄 단위 실행으로 직접 실측 100% 확인(신규 IF-0016~IF-0019 15개 호출지점 전부 포함). 나머지 3개(IF-0010/IF-0011/IF-0012, safety_kernel_orchestrator.py:206-208)는 Phase1부터 이어지는 동일한 coverage.py 도구 한계(runPublishStages()의 람다-튜플 표현식이 물리적으로 여러 줄에걸쳐 있어 개별 statement로 추적되지 않음, ENG-SWE5-001 v0.1 12장 최소 재현 사례로 이미 확인됨 — 코드구조 자체는 Phase2에서 변경되지 않음)로 인해 줄 단위 직접 실측이 불가능하나, IT-0029/IT-0087(recordCalls실물 계측으로 호출 순서 직접 기록)과 IT-0031/IT-0088(Raising* 실물 서브클래스 오류 주입으로 개별 호출과예외 격리를 직접 관측)로 실제 실행을 런타임 증거로 대체 증명 — 이 두 증거를 결합해 총 13개 아키텍처호출관계(IF-0005~IF-0012, IF-0016~IF-0019) 전부 실행 확인(Phase1 9개 + Phase2 신규 4개). 상세는ENG-SWE5-001 v0.2 7장/12장 참조. 적용 한계(12장): SWR-006 override 채널(releaseReRequested)은OEM-FR-001 미분석 placeholder(항상 False)로 고정 — IT-0084가 이 한계를 통합 수준에서 실증 문서화했을뿐, 실제 override 활성화 경로는 OEM-FR-001 분석 이후 재검증 필요. 그 외 Phase1 적용 한계(source_timestamp_s상한, DEGRADED/FAULT 즉시 전이 가정, HIL/실차/SYS.4 범위 밖)는 동일하게 유지.</t>
         </is>
       </c>
     </row>
@@ -2416,7 +4108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2582,6 +4274,38 @@
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C11" s="42" t="inlineStr">
+        <is>
+          <t>integration-tester</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="inlineStr">
+        <is>
+          <t>Phase 2 통합시험 결과 기록 — IT-0044~IT-0093(50건) 전량 실행/Pass, 기존 IT-0020 실제결과갱신(Phase2 신규 계약 관측치로 대체). RUN-SWE5-002 신규 실행 요약 추가(93/93 Pass, 함수/Call커버리지 실측치 포함).</t>
+        </is>
+      </c>
+      <c r="E11" s="42" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F11" s="42" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>

--- a/Deliverables/Engineering/SoftwareComponentVerificationAndIntegrationVerification/ENG-SWE5-003_SW 통합시험 결과서.xlsx
+++ b/Deliverables/Engineering/SoftwareComponentVerificationAndIntegrationVerification/ENG-SWE5-003_SW 통합시험 결과서.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -707,7 +707,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.1 (Draft) — Phase 1 최초 작성</t>
+          <t>v0.3 (Draft) — Phase 3(차량상태 기반 잠금/해제 + ISOFIX 강제잠금) 확장, Phase 1/2 내용 유지</t>
         </is>
       </c>
       <c r="G4" s="9" t="str"/>
@@ -1410,7 +1410,6 @@
           <t>tests_integration/test_it_step4_*.py (unittest 실행, 2026-09-19) + coverage_it.json (test_it_step4_command_arbiter.py, 2026-09-19 갱신)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>해당 없음(Pass)</t>
@@ -3798,6 +3797,1510 @@
       </c>
       <c r="F102" s="42" t="inlineStr"/>
       <c r="G102" s="42" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>IT-0094</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>IF-0023</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>off=True, releaseCandidate(BOTH,RELEASE,4,IGNITION_OFF) 관측 — 기대결과와 일치</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step15_ignition_off_release_monitor.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>IT-0095</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>IF-0023</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>off=False, releaseCandidate=None 관측 — 기대결과와 일치</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step15_ignition_off_release_monitor.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>IT-0096</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>IF-0023</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>예외 없이 off=False 관측 — 8.8절 대칭 결정 실증</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step15_ignition_off_release_monitor.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>IT-0097</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>IF-0023</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ValueError 발생 관측 — 방어적 계약 확인</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step15_ignition_off_release_monitor.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>IT-0098</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>IF-0022</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>양쪽 lockActive=False 관측 — 기대결과와 일치</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step16_isofix_forced_lock_monitor.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>IT-0099</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>IF-0022</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>leftLockCandidate(LEFT,LOCK,5) 관측, right 무영향 — 좌우 독립 확인</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step16_isofix_forced_lock_monitor.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>IT-0100</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>IF-0022</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>rightLockCandidate 관측, left 무영향 — 우측 대칭 확인</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step16_isofix_forced_lock_monitor.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>IT-0101</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>IF-0022</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>양쪽 모두 독립 lockCandidate 관측</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step16_isofix_forced_lock_monitor.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>IT-0102</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>IF-0022</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>예외 없이 leftLockActive=False 관측 — 9장 원칙 실증</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step16_isofix_forced_lock_monitor.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>IT-0103</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>IF-0022</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ValueError 발생 관측</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step16_isofix_forced_lock_monitor.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>IT-0104</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>IF-0021</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>locked=False 관측(2.9km/h) — 경계 하한-1 확인</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step17_vehicle_speed_auto_lock_monitor.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>IT-0105</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>IF-0021</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>locked=True, lockCandidate(BOTH,LOCK,6,AUTO_DRIVE_LOCK) 관측(3.0km/h) — 경계값 자체 확인</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step17_vehicle_speed_auto_lock_monitor.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>IT-0106</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>IF-0021</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>locked=True 관측(3.1km/h) — 경계 상한+1 확인</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step17_vehicle_speed_auto_lock_monitor.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>IT-0107</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>IF-0021</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>예외 없이 locked=False 관측 — 9장 원칙 실증</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step17_vehicle_speed_auto_lock_monitor.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>IT-0108</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>IF-0021</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ValueError 발생 관측</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step17_vehicle_speed_auto_lock_monitor.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>IT-0109</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>IF-0008,IF-0022,IF-0023</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>좌/우 모두 RELEASE, reasonCode=IGNITION_OFF 관측 — 9장 우선순위 체인 확정 실증</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step18_command_arbiter_phase3_priority_chain.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>IT-0110</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>IF-0008,IF-0021,IF-0023</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>좌/우 모두 RELEASE 관측</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step18_command_arbiter_phase3_priority_chain.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>IT-0111</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>IF-0008,IF-0021,IF-0022</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LEFT=LOCK/ISOFIX_FORCED_LOCK_LEFT, RIGHT=LOCK/AUTO_DRIVE_LOCK 관측 — 이유코드 우선순위 확인</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step18_command_arbiter_phase3_priority_chain.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>IT-0112</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>IF-0008,IF-0017,IF-0023</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LEFT=LOCK/APPROACH_RISK_LEFT, RIGHT=RELEASE/IGNITION_OFF 관측 — 갭16 현재 동작 문서화</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step18_command_arbiter_phase3_priority_chain.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass, 갭16 문서화 목적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>IT-0113</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>IF-0008,IF-0019,IF-0022</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>좌/우 모두 RELEASE 관측 — RELEASE계열&gt;LOCK계열 원칙 확인</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step18_command_arbiter_phase3_priority_chain.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>IT-0114</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>IF-0008</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>blocked=True/STATE_FAULT, 좌우 NO_CHANGE 관측 — Phase1 게이트 회귀 없음</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step18_command_arbiter_phase3_priority_chain.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>IT-0115</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>IF-0008</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>blocked=True/INPUT_INVALID 관측 — 결정표 D 회귀 없음</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step18_command_arbiter_phase3_priority_chain.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>IT-0116</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>IF-0008</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ValueError 발생 관측 — 불변조건 신규 priority(5)에도 유지 확인</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step18_command_arbiter_phase3_priority_chain.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>IT-0117</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>IF-0007</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>state=NORMAL 관측 — Phase1 회귀 기준선 확인</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step19_state_manager_off_state.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>IT-0118</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>IF-0007</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>state=OFF, warningReasonCode=IGNITION_OFF 관측</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step19_state_manager_off_state.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>IT-0119</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>IF-0007</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>state=FAULT 관측 — FAULT&gt;OFF 우선순위 확인</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step19_state_manager_off_state.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>IT-0120</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>IF-0007</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>state=OFF 관측 — OFF&gt;DEGRADED 우선순위 확인(갭15 해소 실증)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step19_state_manager_off_state.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>IT-0121</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>IF-0007</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>state=NORMAL 관측(ignitionOnField invalid) — 8.8절 OFF 미판정 결정 실증</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step19_state_manager_off_state.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>IT-0122</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>IF-0007</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ValueError 발생 관측</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step19_state_manager_off_state.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>IT-0123</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>IF-0007</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>8개 조합 전부 결정표 K와 일치(subTest 8/8 통과)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step19_state_manager_off_state.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>IT-0124</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>IF-0001</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>valid=True, value=50.0 관측</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step20_input_validation_adapter_phase3_extended.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>IT-0125</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>IF-0001</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>valid=False, errorReason=OUT_OF_RANGE 관측(-1.0)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step20_input_validation_adapter_phase3_extended.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>IT-0126</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>IF-0001</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>valid=False, errorReason=OUT_OF_RANGE 관측(300.1)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step20_input_validation_adapter_phase3_extended.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>IT-0127</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>IF-0001</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>valid=False, errorReason=TYPE_ERROR 관측</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step20_input_validation_adapter_phase3_extended.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>IT-0128</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>IF-0001</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>valid=False, errorReason=MISSING 관측</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step20_input_validation_adapter_phase3_extended.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>IT-0129</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>IF-0020</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>좌/우 독립 valid=True 관측</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step20_input_validation_adapter_phase3_extended.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>IT-0130</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>IF-0005</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>12필드 전체 정규화 결과 관측 — Phase1/2 필드 회귀 없음</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step20_input_validation_adapter_phase3_extended.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>IT-0131</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>IF-0001~IF-0009,IF-0021</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>confirmedOutput=(LOCK,LOCK) 관측(직전 RELEASE에서 전환) — SWR-003 인수기준 충족</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step21_orchestrator_phase3_integration.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>IT-0132</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>IF-0001~IF-0009,IF-0020,IF-0022</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>confirmedOutput=(LOCK,RELEASE) 관측 — 좌우 독립 실증</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step21_orchestrator_phase3_integration.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>IT-0133</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>IF-0001~IF-0009,IF-0011,IF-0023</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>state=OFF, confirmedOutput=(RELEASE,RELEASE) 관측 — SWR-020 인수기준 충족</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step21_orchestrator_phase3_integration.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>IT-0134</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>IF-0021~IF-0023,IF-0008</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>confirmedOutput=(RELEASE,RELEASE) 관측 — 9장 우선순위 체인 전체 체인 수준 확인</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step21_orchestrator_phase3_integration.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>IT-0135</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>IF-0017,IF-0023,IF-0008</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>confirmedOutput=(LOCK,RELEASE) 관측 — 갭16 현재 동작 전체 체인 수준 문서화</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step21_orchestrator_phase3_integration.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass, 갭16 문서화 목적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>IT-0136</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>IF-0006~IF-0023</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>callLog 14개 항목이 3.1절 고정 순서와 정확히 일치 관측 — Call 커버리지 직접 증명</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step21_orchestrator_phase3_integration.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>IT-0137</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>IF-0005,IF-0008</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>confirmedOutput=(RELEASE,RELEASE) 관측 — 무관 필드 무효가 crash 후보 차단 안함 확인</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step21_orchestrator_phase3_integration.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>IT-0138</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>IF-0005,IF-0008</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>confirmedOutput=(RELEASE,RELEASE) 관측 — 동일 원칙 재확인</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step21_orchestrator_phase3_integration.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>IT-0139</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>IF-0005,IF-0007,IF-0008</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>state=NORMAL, confirmedOutput=(LOCK,LOCK) 관측 — OFF 미판정 회귀 확인(작업 지침 명시 항목)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step21_orchestrator_phase3_integration.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>해당 없음(Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>IT-0140</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>IF-0001,IF-0002,IF-0005,IF-0007,IF-0009</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>state=FAULT, confirmedOutput=(LOCK,LOCK) 관측 — Phase1/2 인수기준 회귀 없음 확인</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>tests_integration/test_it_step21_orchestrator_phase3_integration.py (unittest 실행, 2026-09-20) + coverage_it.json</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
         <is>
           <t>해당 없음(Pass)</t>
         </is>
@@ -3830,7 +5333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3915,7 +5418,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.1 (Draft) — Phase 1 최초 작성</t>
+          <t>v0.3 (Draft) — Phase 3(차량상태 기반 잠금/해제 + ISOFIX 강제잠금) 확장, Phase 1/2 내용 유지</t>
         </is>
       </c>
       <c r="G4" s="9" t="str"/>
@@ -4078,6 +5581,47 @@
       <c r="I11" s="42" t="inlineStr">
         <is>
           <t>함수 커버리지 100%(47/47, 이번 통합 범위 src/ngv 전체 — Phase1 31개+Phase2 신규/갱신 16개 함수, class 선언 제외). 문 커버리지 100%(411/411), 분기 커버리지 100%(76/76) — coverage.py --branch, coverage_it.json(tests_integration/ 93개 케이스 전량 실행 기준, Phase1 43 + Phase2 50). Call 커버리지: AST 매칭 48개 호출지점 중 45개(93.75%)는 coverage.py 줄 단위 실행으로 직접 실측 100% 확인(신규 IF-0016~IF-0019 15개 호출지점 전부 포함). 나머지 3개(IF-0010/IF-0011/IF-0012, safety_kernel_orchestrator.py:206-208)는 Phase1부터 이어지는 동일한 coverage.py 도구 한계(runPublishStages()의 람다-튜플 표현식이 물리적으로 여러 줄에걸쳐 있어 개별 statement로 추적되지 않음, ENG-SWE5-001 v0.1 12장 최소 재현 사례로 이미 확인됨 — 코드구조 자체는 Phase2에서 변경되지 않음)로 인해 줄 단위 직접 실측이 불가능하나, IT-0029/IT-0087(recordCalls실물 계측으로 호출 순서 직접 기록)과 IT-0031/IT-0088(Raising* 실물 서브클래스 오류 주입으로 개별 호출과예외 격리를 직접 관측)로 실제 실행을 런타임 증거로 대체 증명 — 이 두 증거를 결합해 총 13개 아키텍처호출관계(IF-0005~IF-0012, IF-0016~IF-0019) 전부 실행 확인(Phase1 9개 + Phase2 신규 4개). 상세는ENG-SWE5-001 v0.2 7장/12장 참조. 적용 한계(12장): SWR-006 override 채널(releaseReRequested)은OEM-FR-001 미분석 placeholder(항상 False)로 고정 — IT-0084가 이 한계를 통합 수준에서 실증 문서화했을뿐, 실제 override 활성화 경로는 OEM-FR-001 분석 이후 재검증 필요. 그 외 Phase1 적용 한계(source_timestamp_s상한, DEGRADED/FAULT 즉시 전이 가정, HIL/실차/SYS.4 범위 밖)는 동일하게 유지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RUN-SWE5-003</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ENG-SWE2-001 v0.3(Draft) / ENG-SWE3-001 v0.3(구현 기준, coding 2026-09-20 커밋 — 260개 단위+통합+시스템 회귀 전량 Pass 확인 후 본 게이트 착수)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Python 3.12(unittest 실행 인터프리터), coverage.py + radon(python -m radon, PATH 미등록으로 python -m 호출) + ast, tests_integration/(신규 15~21단계 파일 test_it_step15_*~test_it_step21_*.py 포함)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>47</v>
+      </c>
+      <c r="F12" t="n">
+        <v>47</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>전체 회귀 python -m unittest discover -p "test_*.py": 307개(단위137+통합140+시스템30) 전량 Pass (Phase1/2 기존 260개 + Phase3 신규 47개, 회귀 없음). 함수 커버리지 100%(75/75 — src/ngv 전체 15개 파일 + testsupport/orchestrator_factory.py, Phase3 관련 7개 파일 41개 함수 포함, class 선언 제외). 문/분기 커버리지 100%(coverage.py --branch --source=src/ngv,testsupport, 전 파일 percent_covered=100.0). Call 커버리지: AST(ast.Call) 매칭 38개 호출지점 중 34개(89.5%)는 coverage.py 줄 단위 실행으로 직접 실측 100% 확인(신규 IF-0021~IF-0023 15개 호출지점, IU-0014/0015/0016 내부 buildLockCandidate/evaluateSide/buildReleaseCandidate 호출지점, IU-0003 decideState/decideWarningReasonCode 호출지점, IU-0001 normalizeCycle() 내부 12개 검증함수 호출지점 전부 포함). 나머지 4개(safety_kernel_orchestrator.py 의 publish/publishWarning/log — Phase1/2부터 이어지는 동일한 람다-튜플 표현식 도구 한계, 코드 미변경 + assemblePhase3Candidates 호출지점 — candidates.extend(...) 다줄 호출식이 동일한 종류의 coverage.py 물리줄 귀속 한계에 새로 해당됨, 193행)는 줄 단위 직접 실측이 불가능하나, IT-0136(recordCalls 실물 계측으로 14개 호출 전부 순서까지 기록, publish/publishWarning/log 포함)과 IT-0131~0135(Phase3 전용 후보만으로 실제 출력이 전환되는 것을 관측 — assemblePhase3Candidates가 실행되지 않았다면 재현 불가능한 결과)로 런타임 증거를 통해 실제 실행을 직접 증명해 보완 — 38개 아키텍처 호출관계 전부 실행 확인 완료. 신규 갭: 없음(Phase3 SWE.1~SWE.4에서 이미 식별된 갭 12/14/16/17을 그대로 재확인·유지). 이번 게이트에서 '현재 동작 문서화' 성격으로 다룬 항목: 갭16(접근위험 ASIL B priority=2 vs ignition-off QM priority=4 동시 성립 시 접근위험 승리, IT-0112/IT-0135) — 이 우선순위 관계가 OEM-A로 최종 확정된 것이라고 단정하지 않으며, 회귀 고정은 향후 코드 변경 시 이 관계가 의도치 않게 바뀌지 않았는지 감지하기 위한 목적이다. coding 게이트가 기계적으로 동기화한 test_it_step6/14의 Phase3 3개 협력객체(vehicleSpeedMonitor/isofixMonitor/ignitionOffReleaseMonitor) 배선을 재확인 — buildOrchestratorKwargs()/buildPhase2Collaborators()(Phase3 포함 명명은 유지) 모두 정확함을 확인, 정정 불필요. 적용 한계(12장): Phase1/2 적용 한계(source_timestamp_s 상한, DEGRADED/FAULT 즉시 전이 가정, releaseReRequested placeholder, HIL/실차/SYS.4 범위 밖)는 동일하게 유지. Phase3 신규 적용 한계: SWR-018 해제요청 억제 여부(갭14), SWR-003 하강 시 자동 RELEASE 복귀 여부(갭17), gear 필드 미사용(갭12)은 통합시험 범위에서 다루지 않음(SWE.1/SWE.2 갭 그대로 승계, 코드에 해당 로직 자체가 없어 시험 대상 없음).</t>
         </is>
       </c>
     </row>
@@ -4108,7 +5652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4187,7 +5731,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.1 (Draft) — Phase 1 최초 작성</t>
+          <t>v0.3 (Draft) — Phase 3(차량상태 기반 잠금/해제 + ISOFIX 강제잠금) 확장, Phase 1/2 내용 유지</t>
         </is>
       </c>
     </row>
@@ -4306,6 +5850,38 @@
         </is>
       </c>
       <c r="F11" s="42" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>integration-tester</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Phase 3 확장 — IT-0094~IT-0140(47건) 결과 기록(전량 Pass), RUN-SWE5-003 요약 추가(함수 커버리지 100%[75/75], Call 커버리지 38/38[34 직접실측 + 4 런타임증거보완]).</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>
